--- a/Resources/main_template.xlsx
+++ b/Resources/main_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaewo\Desktop\work\mapper\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBACA9B-70A0-40A9-B47C-2CE942E9094E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD945272-45A4-4D83-A947-16B0E57DBE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="948" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="948" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main 작성요령" sheetId="33" r:id="rId1"/>
@@ -486,12 +486,95 @@
         </r>
       </text>
     </comment>
+    <comment ref="O14" authorId="0" shapeId="0" xr:uid="{BDB8EFE3-654D-44D5-9491-4FD4F30C12BE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>김재원</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>요약</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>시트에서</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="285">
   <si>
     <t>2. 국가별 적용면제 및 제외</t>
   </si>
@@ -1581,10 +1664,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>첨부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>2.소득산입보완규칙
 추가세액배분액
 전기이월액</t>
@@ -1621,6 +1700,30 @@
   </si>
   <si>
     <t>GIR301</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GIR301: Constituent Entity
+GIR302: Flow-Through Entity - Tax Transparent
+GIR303: Flow-Through Entity - Reverse Hybrid
+GIR304: Hybrid Entity
+GIR305: Permanent Establishment
+GIR306: Main Entity
+GIR307: Minority-Owned Parent Entity
+GIR308: Minority-Owned Subsidiary
+GIR309: Minority-Owned Constituent Entity
+GIR310: Investment Entity
+GIR311: Insurance Investment Entity
+GIR312: Securitisation Entity
+GIR313: JV
+GIR314: JV Subsidiary
+GIR315: Non-Material Constituent Entity
+GIR316: Excluded Entity
+GIR317: Parent Entity required to apply a QIIR under Article 10.3.5
+GIR318: Non-group Member</t>
+  </si>
+  <si>
+    <t>첨부1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1770,7 +1873,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -2075,17 +2178,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2244,9 +2336,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2277,9 +2366,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2319,15 +2405,28 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2340,28 +2439,52 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2371,58 +2494,22 @@
       <alignment horizontal="distributed" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2431,188 +2518,191 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="35" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="30" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="36" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="31" xfId="2" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -2956,694 +3046,694 @@
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19.0703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="64.78515625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="67.7109375" style="22" customWidth="1"/>
-    <col min="6" max="6" width="22.2109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.0703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="64.78515625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="67.7109375" style="20" customWidth="1"/>
+    <col min="6" max="6" width="22.2109375" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="22" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="15"/>
+    </row>
+    <row r="5" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="15"/>
+    </row>
+    <row r="12" spans="2:6" ht="369" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="15"/>
+    </row>
+    <row r="19" spans="2:6" ht="316.3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="F22" s="15"/>
+    </row>
+    <row r="23" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="F23" s="15"/>
+    </row>
+    <row r="24" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="F25" s="15"/>
+    </row>
+    <row r="26" spans="2:6" ht="140.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F26" s="15"/>
+    </row>
+    <row r="27" spans="2:6" ht="35.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="E27" s="24" t="s">
         <v>280</v>
       </c>
-      <c r="F3" s="16"/>
-    </row>
-    <row r="4" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4" s="25" t="s">
+      <c r="F27" s="15"/>
+    </row>
+    <row r="28" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D28" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E28" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="F4" s="16"/>
-    </row>
-    <row r="5" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5" s="16"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="E6" s="26" t="s">
+      <c r="F28" s="15"/>
+    </row>
+    <row r="29" spans="2:6" ht="369" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="140.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="F30" s="15"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="E31" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="F6" s="16"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="16"/>
-    </row>
-    <row r="8" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="F8" s="16"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="16"/>
-    </row>
-    <row r="10" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="F10" s="16" t="s">
+      <c r="F31" s="15"/>
+    </row>
+    <row r="32" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F32" s="15"/>
+    </row>
+    <row r="33" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="F33" s="15"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F34" s="15" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="26" t="s">
+    <row r="35" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="246" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F39" s="15"/>
+    </row>
+    <row r="40" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F40" s="15"/>
+    </row>
+    <row r="41" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="E41" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="F11" s="16"/>
-    </row>
-    <row r="12" spans="2:6" ht="369" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="F13" s="16"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="D15" s="25" t="s">
+      <c r="F41" s="15"/>
+    </row>
+    <row r="42" spans="2:6" ht="333.9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F43" s="15"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="D44" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="F17" s="16"/>
-    </row>
-    <row r="18" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="F18" s="16"/>
-    </row>
-    <row r="19" spans="2:6" ht="369" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F20" s="16"/>
-    </row>
-    <row r="21" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="F22" s="16"/>
-    </row>
-    <row r="23" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="F23" s="16"/>
-    </row>
-    <row r="24" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="F24" s="16"/>
-    </row>
-    <row r="25" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="F25" s="16"/>
-    </row>
-    <row r="26" spans="2:6" ht="140.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="F26" s="16"/>
-    </row>
-    <row r="27" spans="2:6" ht="35.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="F27" s="16"/>
-    </row>
-    <row r="28" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="F28" s="16"/>
-    </row>
-    <row r="29" spans="2:6" ht="369" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" ht="140.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="F30" s="16"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="F31" s="16"/>
-    </row>
-    <row r="32" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="F32" s="16"/>
-    </row>
-    <row r="33" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="F33" s="16"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="E34" s="26" t="s">
+      <c r="E44" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="F34" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="246" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="F36" s="16"/>
-    </row>
-    <row r="37" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="F37" s="16"/>
-    </row>
-    <row r="38" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="F38" s="16"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="E39" s="26" t="s">
+      <c r="F44" s="15"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="E45" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="F39" s="16"/>
-    </row>
-    <row r="40" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="F40" s="16"/>
-    </row>
-    <row r="41" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="F41" s="16"/>
-    </row>
-    <row r="42" spans="2:6" ht="333.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F43" s="16"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="E44" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F44" s="16"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>278</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F45" s="16"/>
+      <c r="F45" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3656,7 +3746,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="B2:C3"/>
+  <dimension ref="B2:C5"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
@@ -3664,16 +3754,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="30" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3714,138 +3809,144 @@
   <sheetData>
     <row r="1" spans="2:18" ht="7.85" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="2" spans="2:18" ht="22.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
       <c r="R2" s="34"/>
     </row>
     <row r="3" spans="2:18" ht="90" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37" t="s">
+      <c r="C3" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40" t="s">
         <v>127</v>
       </c>
       <c r="F3" s="34"/>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="H3" s="33"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="34"/>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="41" t="s">
         <v>129</v>
       </c>
       <c r="K3" s="34"/>
-      <c r="L3" s="38" t="s">
+      <c r="L3" s="41" t="s">
         <v>130</v>
       </c>
       <c r="M3" s="34"/>
-      <c r="N3" s="35" t="s">
+      <c r="N3" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="39" t="s">
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="R3" s="40"/>
+      <c r="R3" s="43"/>
     </row>
     <row r="4" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="41"/>
+      <c r="C4" s="150">
+        <v>0</v>
+      </c>
+      <c r="D4" s="151"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="34"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="32"/>
       <c r="I4" s="34"/>
-      <c r="J4" s="42"/>
+      <c r="J4" s="35"/>
       <c r="K4" s="34"/>
-      <c r="L4" s="41"/>
+      <c r="L4" s="33"/>
       <c r="M4" s="34"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="33"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="32"/>
     </row>
     <row r="5" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="2"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="41"/>
+      <c r="C5" s="150">
+        <v>0</v>
+      </c>
+      <c r="D5" s="151"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="34"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="32"/>
       <c r="I5" s="34"/>
-      <c r="J5" s="42"/>
+      <c r="J5" s="35"/>
       <c r="K5" s="34"/>
-      <c r="L5" s="41"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="34"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="33"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="32"/>
     </row>
     <row r="6" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="41"/>
+      <c r="C6" s="150">
+        <v>0</v>
+      </c>
+      <c r="D6" s="151"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="34"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="32"/>
       <c r="I6" s="34"/>
-      <c r="J6" s="42"/>
+      <c r="J6" s="35"/>
       <c r="K6" s="34"/>
-      <c r="L6" s="41"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="34"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="33"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="32"/>
     </row>
     <row r="7" spans="2:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
     </row>
     <row r="8" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="9" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -3854,8 +3955,8 @@
     <row r="12" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="13" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="14" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="F14" s="19"/>
-      <c r="K14" s="19"/>
+      <c r="F14" s="17"/>
+      <c r="K14" s="17"/>
     </row>
     <row r="15" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="16" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -3874,6 +3975,19 @@
     <row r="29" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
     <mergeCell ref="N5:P5"/>
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="Q4:R4"/>
@@ -3890,19 +4004,6 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:M5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="B2:R2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -4057,420 +4158,443 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="23.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="62">
+      <c r="C2" s="72">
         <v>45292</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="72" t="s">
+      <c r="D2" s="70"/>
+      <c r="E2" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="54" t="s">
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="55"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
     </row>
     <row r="3" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="49"/>
-      <c r="C3" s="48" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="49"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="61"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
     </row>
     <row r="4" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="49"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="54" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="55"/>
-      <c r="P4" s="70"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
     </row>
     <row r="5" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="57"/>
-      <c r="C5" s="69">
+      <c r="B5" s="45"/>
+      <c r="C5" s="44">
         <v>45657</v>
       </c>
-      <c r="D5" s="57"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
     </row>
     <row r="6" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="46"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="52"/>
     </row>
     <row r="7" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="55"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="70"/>
     </row>
     <row r="8" spans="2:18" ht="36.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="60" t="s">
         <v>49</v>
       </c>
       <c r="C8" s="34"/>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
       <c r="G8" s="34"/>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="33"/>
+      <c r="I8" s="32"/>
       <c r="J8" s="34"/>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="40" t="s">
         <v>52</v>
       </c>
       <c r="L8" s="34"/>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="40" t="s">
         <v>53</v>
       </c>
       <c r="N8" s="34"/>
-      <c r="O8" s="38" t="s">
+      <c r="O8" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
       <c r="R8" s="34"/>
     </row>
     <row r="9" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="60" t="s">
         <v>154</v>
       </c>
       <c r="C9" s="34"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="38" t="s">
+      <c r="D9" s="62"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="41" t="s">
         <v>158</v>
       </c>
       <c r="L9" s="34"/>
-      <c r="M9" s="38" t="s">
+      <c r="M9" s="41" t="s">
         <v>155</v>
       </c>
       <c r="N9" s="34"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
       <c r="R9" s="34"/>
     </row>
     <row r="10" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="44"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="46"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="52"/>
     </row>
     <row r="11" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="46"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="52"/>
     </row>
     <row r="12" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="46"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="52"/>
     </row>
     <row r="13" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="58" t="s">
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="58" t="s">
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="58" t="s">
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="46"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="52"/>
     </row>
     <row r="14" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="47">
-        <f>D9</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="65">
+      <c r="B14" s="50"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="59">
         <v>45292</v>
       </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="65">
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="59">
         <v>45657</v>
       </c>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="58" t="s">
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="46"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="52"/>
     </row>
     <row r="15" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="46"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="51"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="52"/>
     </row>
     <row r="16" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="58" t="s">
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="58" t="s">
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="46"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="51"/>
+      <c r="R16" s="52"/>
     </row>
     <row r="17" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="58" t="s">
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="58" t="s">
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="46"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="51"/>
+      <c r="R17" s="52"/>
     </row>
     <row r="18" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="44"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="46"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="51"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="51"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="52"/>
     </row>
     <row r="19" spans="2:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B18:R18"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="N2:O3"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="P2:R3"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="N4:O5"/>
+    <mergeCell ref="B7:R7"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="M17:R17"/>
+    <mergeCell ref="B10:R10"/>
+    <mergeCell ref="M16:R16"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="K13:N13"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="P4:R5"/>
     <mergeCell ref="B16:G16"/>
@@ -4487,32 +4611,6 @@
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="B12:R12"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="M17:R17"/>
-    <mergeCell ref="B10:R10"/>
-    <mergeCell ref="M16:R16"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="B18:R18"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="N2:O3"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="P2:R3"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="N4:O5"/>
-    <mergeCell ref="B7:R7"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="H16:L16"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
@@ -4557,252 +4655,259 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
     </row>
     <row r="3" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
     </row>
     <row r="4" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="76" t="s">
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
     </row>
     <row r="5" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="76" t="s">
-        <v>279</v>
-      </c>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="74" t="s">
+        <v>278</v>
+      </c>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
     </row>
     <row r="6" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="74" t="s">
+      <c r="B6" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="76">
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="74">
         <f>'다국적기업그룹 정보'!D9</f>
         <v>0</v>
       </c>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
     </row>
     <row r="7" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="80">
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="79">
         <f>'다국적기업그룹 정보'!H9</f>
         <v>0</v>
       </c>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="81"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="80"/>
     </row>
     <row r="8" spans="2:18" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="84"/>
-      <c r="K8" s="85"/>
-      <c r="L8" s="85"/>
-      <c r="M8" s="85"/>
-      <c r="N8" s="85"/>
-      <c r="O8" s="85"/>
-      <c r="P8" s="85"/>
-      <c r="Q8" s="85"/>
-      <c r="R8" s="85"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="84"/>
+      <c r="O8" s="84"/>
+      <c r="P8" s="84"/>
+      <c r="Q8" s="84"/>
+      <c r="R8" s="84"/>
     </row>
     <row r="9" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="76" t="s">
-        <v>283</v>
-      </c>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="60"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="74" t="s">
+        <v>282</v>
+      </c>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="47"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
     </row>
     <row r="10" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="76"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="60"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="60"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
     </row>
     <row r="11" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="82" t="s">
+      <c r="B11" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="79"/>
-      <c r="R11" s="79"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="78"/>
     </row>
     <row r="12" spans="2:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="F14" s="19"/>
-      <c r="K14" s="19"/>
+      <c r="F14" s="17"/>
+      <c r="K14" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="J6:R6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="J4:R4"/>
+    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="B3:R3"/>
+    <mergeCell ref="J5:R5"/>
     <mergeCell ref="J10:R10"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B5:I5"/>
@@ -4814,13 +4919,6 @@
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="J8:R8"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="J6:R6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="J4:R4"/>
-    <mergeCell ref="B2:R2"/>
-    <mergeCell ref="B3:R3"/>
-    <mergeCell ref="J5:R5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -4860,420 +4958,447 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="93"/>
-      <c r="R2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="87"/>
     </row>
     <row r="3" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="93"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="87"/>
     </row>
     <row r="4" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="98" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="93"/>
-      <c r="D4" s="90" t="s">
+      <c r="C4" s="87"/>
+      <c r="D4" s="106" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
       <c r="N4" s="89"/>
-      <c r="O4" s="92"/>
-      <c r="P4" s="93"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="93"/>
+      <c r="O4" s="91" t="s">
+        <v>156</v>
+      </c>
+      <c r="P4" s="87"/>
+      <c r="Q4" s="87"/>
+      <c r="R4" s="87"/>
     </row>
     <row r="5" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="100"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="89"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="93"/>
-      <c r="Q5" s="93"/>
-      <c r="R5" s="93"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
+      <c r="R5" s="87"/>
     </row>
     <row r="6" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="40"/>
-      <c r="C6" s="101"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="102"/>
       <c r="D6" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
       <c r="N6" s="89"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="93"/>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="93"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="87"/>
+      <c r="Q6" s="87"/>
+      <c r="R6" s="87"/>
     </row>
     <row r="7" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="99" t="s">
+      <c r="B7" s="98" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="100"/>
+      <c r="C7" s="99"/>
       <c r="D7" s="88" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
       <c r="N7" s="89"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="93"/>
-      <c r="R7" s="93"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="87"/>
+      <c r="R7" s="87"/>
     </row>
     <row r="8" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="73"/>
-      <c r="C8" s="102"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="101"/>
       <c r="D8" s="88" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
       <c r="N8" s="89"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="95"/>
-      <c r="Q8" s="95"/>
-      <c r="R8" s="95"/>
+      <c r="O8" s="107"/>
+      <c r="P8" s="97"/>
+      <c r="Q8" s="97"/>
+      <c r="R8" s="97"/>
     </row>
     <row r="9" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="73"/>
-      <c r="C9" s="102"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="101"/>
       <c r="D9" s="88" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
       <c r="N9" s="89"/>
-      <c r="O9" s="108"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="109"/>
-      <c r="R9" s="109"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="95"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="95"/>
     </row>
     <row r="10" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="40"/>
-      <c r="C10" s="101"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="102"/>
       <c r="D10" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
       <c r="N10" s="89"/>
-      <c r="O10" s="92"/>
-      <c r="P10" s="93"/>
-      <c r="Q10" s="93"/>
-      <c r="R10" s="93"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="87"/>
+      <c r="Q10" s="87"/>
+      <c r="R10" s="87"/>
     </row>
     <row r="11" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="99" t="s">
+      <c r="B11" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="100"/>
+      <c r="C11" s="99"/>
       <c r="D11" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
       <c r="N11" s="89"/>
-      <c r="O11" s="92" t="s">
+      <c r="O11" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="P11" s="92"/>
-      <c r="Q11" s="92"/>
-      <c r="R11" s="92"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
+      <c r="R11" s="91"/>
     </row>
     <row r="12" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="73"/>
-      <c r="C12" s="102"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="101"/>
       <c r="D12" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="91"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
       <c r="N12" s="89"/>
-      <c r="O12" s="86"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="86"/>
+      <c r="O12" s="104"/>
+      <c r="P12" s="104"/>
+      <c r="Q12" s="104"/>
+      <c r="R12" s="104"/>
     </row>
     <row r="13" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="73"/>
-      <c r="C13" s="102"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="101"/>
       <c r="D13" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="93"/>
       <c r="N13" s="89"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="86"/>
-      <c r="Q13" s="86"/>
-      <c r="R13" s="86"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="104"/>
     </row>
     <row r="14" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="40"/>
-      <c r="C14" s="101"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="102"/>
       <c r="D14" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
       <c r="N14" s="89"/>
-      <c r="O14" s="86"/>
-      <c r="P14" s="86"/>
-      <c r="Q14" s="86"/>
-      <c r="R14" s="86"/>
+      <c r="O14" s="104"/>
+      <c r="P14" s="104"/>
+      <c r="Q14" s="104"/>
+      <c r="R14" s="104"/>
     </row>
     <row r="15" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="99" t="s">
+      <c r="B15" s="98" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="100"/>
-      <c r="D15" s="99" t="s">
+      <c r="C15" s="99"/>
+      <c r="D15" s="98" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="93"/>
-      <c r="K15" s="93"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="100"/>
-      <c r="O15" s="86"/>
-      <c r="P15" s="87"/>
-      <c r="Q15" s="87"/>
-      <c r="R15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="104"/>
+      <c r="P15" s="105"/>
+      <c r="Q15" s="105"/>
+      <c r="R15" s="105"/>
     </row>
     <row r="16" spans="2:18" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="73"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="99" t="s">
+      <c r="B16" s="58"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="100"/>
-      <c r="O16" s="94"/>
-      <c r="P16" s="95"/>
-      <c r="Q16" s="95"/>
-      <c r="R16" s="95"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="97"/>
+      <c r="Q16" s="97"/>
+      <c r="R16" s="97"/>
     </row>
     <row r="17" spans="2:18" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="40"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="104" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="103" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
       <c r="N17" s="89"/>
-      <c r="O17" s="94"/>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="95"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="97"/>
+      <c r="Q17" s="97"/>
+      <c r="R17" s="97"/>
     </row>
     <row r="18" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="99" t="s">
+      <c r="B18" s="98" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="100"/>
-      <c r="D18" s="103" t="s">
+      <c r="C18" s="99"/>
+      <c r="D18" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="100"/>
-      <c r="O18" s="107"/>
-      <c r="P18" s="93"/>
-      <c r="Q18" s="93"/>
-      <c r="R18" s="93"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="92" t="s">
+        <v>156</v>
+      </c>
+      <c r="P18" s="87"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="87"/>
     </row>
     <row r="19" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="73"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="103" t="s">
+      <c r="B19" s="58"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="100" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="87"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="109"/>
     </row>
     <row r="20" spans="2:18" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="40"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="106" t="s">
+      <c r="B20" s="43"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
       <c r="N20" s="89"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="D14:N14"/>
+    <mergeCell ref="D4:N4"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="D13:N13"/>
+    <mergeCell ref="D8:N8"/>
+    <mergeCell ref="D11:N11"/>
+    <mergeCell ref="D7:N7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="O11:R14"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B15:C17"/>
+    <mergeCell ref="D18:N18"/>
+    <mergeCell ref="D9:N9"/>
+    <mergeCell ref="D15:N15"/>
+    <mergeCell ref="D6:N6"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="D17:N17"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="D5:N5"/>
     <mergeCell ref="D20:N20"/>
@@ -5290,29 +5415,6 @@
     <mergeCell ref="B11:C14"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B7:C10"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B15:C17"/>
-    <mergeCell ref="D18:N18"/>
-    <mergeCell ref="D9:N9"/>
-    <mergeCell ref="D15:N15"/>
-    <mergeCell ref="D6:N6"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="D17:N17"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="D14:N14"/>
-    <mergeCell ref="D4:N4"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="D13:N13"/>
-    <mergeCell ref="D8:N8"/>
-    <mergeCell ref="D11:N11"/>
-    <mergeCell ref="D7:N7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="O11:R14"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
@@ -5333,17 +5435,17 @@
   <dimension ref="B2:K15"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="3" width="13.140625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="28" customWidth="1"/>
+    <col min="2" max="3" width="13.140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" s="17"/>
+      <c r="C3" s="16"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="6" t="s">
@@ -5358,15 +5460,15 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="6"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="27"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" s="17"/>
+      <c r="C6" s="16"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="F15" s="20"/>
-      <c r="K15" s="20"/>
+      <c r="F15" s="18"/>
+      <c r="K15" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5409,92 +5511,94 @@
       <c r="B2" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="93"/>
-      <c r="R2" s="93"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="87"/>
     </row>
     <row r="3" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="112" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="93"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="92" t="s">
+        <v>156</v>
+      </c>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="87"/>
     </row>
     <row r="4" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="111" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
     </row>
     <row r="5" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="111" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" s="19"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="F15" s="19"/>
-      <c r="K15" s="19"/>
+      <c r="F15" s="17"/>
+      <c r="K15" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5545,128 +5649,146 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="121"/>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="121"/>
-      <c r="R2" s="121"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="124"/>
     </row>
     <row r="3" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="122" t="s">
+      <c r="C3" s="125" t="s">
         <v>161</v>
       </c>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="120"/>
-      <c r="R3" s="120"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
     </row>
     <row r="4" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="5" spans="2:18" ht="100.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="124" t="s">
+      <c r="B5" s="128" t="s">
         <v>226</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="125" t="s">
+      <c r="C5" s="89"/>
+      <c r="D5" s="129" t="s">
         <v>110</v>
       </c>
       <c r="E5" s="34"/>
-      <c r="F5" s="126" t="s">
+      <c r="F5" s="120" t="s">
         <v>111</v>
       </c>
       <c r="G5" s="34"/>
-      <c r="H5" s="126" t="s">
+      <c r="H5" s="120" t="s">
         <v>112</v>
       </c>
       <c r="I5" s="34"/>
-      <c r="J5" s="117" t="s">
+      <c r="J5" s="126" t="s">
         <v>113</v>
       </c>
-      <c r="K5" s="118"/>
-      <c r="L5" s="123"/>
-      <c r="M5" s="117" t="s">
+      <c r="K5" s="127"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="N5" s="118"/>
-      <c r="O5" s="123"/>
-      <c r="P5" s="117" t="s">
+      <c r="N5" s="127"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="126" t="s">
         <v>233</v>
       </c>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
+      <c r="Q5" s="127"/>
+      <c r="R5" s="127"/>
     </row>
     <row r="6" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="124"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="127"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="119"/>
       <c r="G6" s="34"/>
-      <c r="H6" s="126"/>
+      <c r="H6" s="120"/>
       <c r="I6" s="34"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="116"/>
-      <c r="O6" s="116"/>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="120"/>
-      <c r="R6" s="120"/>
-    </row>
-    <row r="8" spans="2:18" ht="19.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="113"/>
+      <c r="N6" s="113"/>
+      <c r="O6" s="113"/>
+      <c r="P6" s="114"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115"/>
+    </row>
+    <row r="7" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="94"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="121"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="113"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="113"/>
+      <c r="P7" s="114"/>
+      <c r="Q7" s="115"/>
+      <c r="R7" s="115"/>
+    </row>
+    <row r="8" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="116"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="122"/>
+      <c r="L8" s="123"/>
+      <c r="M8" s="113"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="114"/>
+      <c r="Q8" s="115"/>
+      <c r="R8" s="115"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="F15" s="19"/>
-      <c r="J15" s="19"/>
+      <c r="F15" s="17"/>
+      <c r="J15" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="P6:R6"/>
+  <mergeCells count="31">
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="C3:P3"/>
@@ -5675,13 +5797,32 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="P6:R6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:L7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:R3" xr:uid="{CE837DA2-832B-4ACA-AE98-1418B45B4442}">
       <formula1>"여,부"</formula1>
     </dataValidation>
@@ -5730,111 +5871,144 @@
       <c r="B2" s="110" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
     </row>
     <row r="3" spans="2:19" ht="72.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="28" t="s">
         <v>116</v>
       </c>
       <c r="C3" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="101"/>
+      <c r="D3" s="102"/>
       <c r="E3" s="131" t="s">
         <v>118</v>
       </c>
-      <c r="F3" s="101"/>
+      <c r="F3" s="102"/>
       <c r="G3" s="131" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="101"/>
+      <c r="H3" s="102"/>
       <c r="I3" s="131" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="101"/>
+      <c r="J3" s="102"/>
       <c r="K3" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="L3" s="101"/>
+      <c r="L3" s="102"/>
       <c r="M3" s="131" t="s">
         <v>122</v>
       </c>
-      <c r="N3" s="101"/>
+      <c r="N3" s="102"/>
       <c r="O3" s="131" t="s">
         <v>256</v>
       </c>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="129" t="s">
+      <c r="P3" s="102"/>
+      <c r="Q3" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="R3" s="40"/>
+      <c r="R3" s="43"/>
       <c r="S3" s="4"/>
     </row>
     <row r="4" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="1"/>
-      <c r="C4" s="126"/>
+      <c r="C4" s="120"/>
       <c r="D4" s="34"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="126"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="120"/>
       <c r="H4" s="34"/>
-      <c r="I4" s="126"/>
+      <c r="I4" s="120"/>
       <c r="J4" s="34"/>
-      <c r="K4" s="126"/>
+      <c r="K4" s="120"/>
       <c r="L4" s="34"/>
-      <c r="M4" s="126"/>
+      <c r="M4" s="120"/>
       <c r="N4" s="34"/>
-      <c r="O4" s="126"/>
+      <c r="O4" s="120"/>
       <c r="P4" s="34"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="33"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="32"/>
       <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="2:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="8"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
+    <row r="5" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="1"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="120"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="126"/>
+      <c r="R5" s="32"/>
+    </row>
+    <row r="6" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="1"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="120"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="120"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="120"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="32"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="F14" s="19"/>
-      <c r="K14" s="19"/>
+      <c r="F14" s="17"/>
+      <c r="K14" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="I4:J4"/>
+  <mergeCells count="33">
+    <mergeCell ref="O5:P5"/>
     <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q5:R5"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="Q4:R4"/>
     <mergeCell ref="E3:F3"/>
@@ -5847,10 +6021,12 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4:N4" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4:N6" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"여,부"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5868,7 +6044,7 @@
     <tabColor theme="3" tint="0.89999084444715716"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:R51"/>
+  <dimension ref="B2:R50"/>
   <sheetFormatPr defaultColWidth="8.78515625" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2" style="3" customWidth="1"/>
@@ -5893,189 +6069,188 @@
     <col min="22" max="16384" width="8.78515625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="7.85" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="2" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
       <c r="R2" s="34"/>
     </row>
     <row r="3" spans="2:18" ht="40.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
       <c r="R3" s="34"/>
     </row>
     <row r="4" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
       <c r="R4" s="34"/>
     </row>
     <row r="5" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="34"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
       <c r="R5" s="34"/>
     </row>
     <row r="6" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
       <c r="N6" s="34"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
       <c r="R6" s="34"/>
     </row>
     <row r="7" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
       <c r="N7" s="34"/>
       <c r="O7" s="143"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="53"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="68"/>
     </row>
     <row r="8" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
       <c r="N8" s="34"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
       <c r="R8" s="34"/>
     </row>
     <row r="9" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
       <c r="N9" s="34"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="140"/>
-      <c r="Q9" s="140"/>
-      <c r="R9" s="141"/>
-    </row>
-    <row r="10" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
+      <c r="O9" s="140"/>
+      <c r="P9" s="141"/>
+      <c r="Q9" s="141"/>
+      <c r="R9" s="36"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
@@ -6085,856 +6260,789 @@
       <c r="B11" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
       <c r="R11" s="34"/>
     </row>
     <row r="12" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
       <c r="R12" s="34"/>
     </row>
     <row r="13" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
       <c r="R13" s="34"/>
     </row>
     <row r="14" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
       <c r="N14" s="34"/>
-      <c r="O14" s="139" t="str">
-        <f>IF(요약!I4&lt;&gt;0, 요약!I4, "")</f>
-        <v/>
-      </c>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="140"/>
-      <c r="R14" s="141"/>
+      <c r="O14" s="140"/>
+      <c r="P14" s="141"/>
+      <c r="Q14" s="141"/>
+      <c r="R14" s="36"/>
     </row>
     <row r="15" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
       <c r="R15" s="34"/>
     </row>
     <row r="16" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
       <c r="R16" s="34"/>
     </row>
     <row r="17" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="137"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
+      <c r="B17" s="142"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
       <c r="G17" s="34"/>
-      <c r="H17" s="37" t="s">
+      <c r="H17" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
       <c r="M17" s="34"/>
-      <c r="N17" s="38" t="s">
+      <c r="N17" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
       <c r="R17" s="34"/>
     </row>
     <row r="18" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="137" t="s">
+      <c r="B18" s="142" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
       <c r="G18" s="34"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
       <c r="M18" s="34"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
       <c r="R18" s="34"/>
     </row>
     <row r="19" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="137" t="s">
+      <c r="B19" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
       <c r="G19" s="34"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
       <c r="M19" s="34"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
       <c r="R19" s="34"/>
     </row>
     <row r="20" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="137" t="s">
+      <c r="B20" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
       <c r="G20" s="34"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
       <c r="M20" s="34"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
       <c r="R20" s="34"/>
     </row>
     <row r="21" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="137" t="s">
+      <c r="B21" s="142" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
       <c r="G21" s="34"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
       <c r="M21" s="34"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
       <c r="R21" s="34"/>
     </row>
-    <row r="22" spans="2:18" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B22" s="150"/>
-      <c r="C22" s="151"/>
-      <c r="D22" s="151"/>
-      <c r="E22" s="151"/>
-      <c r="F22" s="151"/>
-      <c r="G22" s="151"/>
-      <c r="H22" s="151"/>
-      <c r="I22" s="151"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
+    <row r="23" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="138" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="34"/>
     </row>
     <row r="24" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="138" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
+        <v>21</v>
+      </c>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
       <c r="R24" s="34"/>
     </row>
     <row r="25" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="138" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
+      <c r="B25" s="139" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="34"/>
       <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
       <c r="R25" s="34"/>
     </row>
     <row r="26" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="136" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
+      <c r="B26" s="139" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
       <c r="N26" s="34"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
       <c r="R26" s="34"/>
     </row>
     <row r="27" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="136" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
+      <c r="B27" s="139" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
       <c r="N27" s="34"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
       <c r="R27" s="34"/>
     </row>
-    <row r="28" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="136" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="34"/>
-    </row>
-    <row r="29" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="29" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="138" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="34"/>
+    </row>
     <row r="30" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="138" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33"/>
+      <c r="B30" s="139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="147"/>
+      <c r="P30" s="32"/>
+      <c r="Q30" s="32"/>
       <c r="R30" s="34"/>
     </row>
-    <row r="31" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="136" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="142"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="34"/>
-    </row>
-    <row r="32" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="32" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="138" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="34"/>
+    </row>
     <row r="33" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="138" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="34"/>
+      <c r="B33" s="145" t="s">
+        <v>269</v>
+      </c>
+      <c r="C33" s="145"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="145"/>
+      <c r="H33" s="145"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="145"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="145"/>
+      <c r="M33" s="145"/>
+      <c r="N33" s="145"/>
+      <c r="O33" s="145"/>
+      <c r="P33" s="145"/>
+      <c r="Q33" s="145"/>
+      <c r="R33" s="146"/>
     </row>
     <row r="34" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="132" t="s">
-        <v>269</v>
-      </c>
-      <c r="C34" s="132"/>
-      <c r="D34" s="132"/>
-      <c r="E34" s="132"/>
-      <c r="F34" s="132"/>
-      <c r="G34" s="132"/>
-      <c r="H34" s="132"/>
-      <c r="I34" s="132"/>
-      <c r="J34" s="132"/>
-      <c r="K34" s="132"/>
-      <c r="L34" s="132"/>
-      <c r="M34" s="132"/>
-      <c r="N34" s="132"/>
-      <c r="O34" s="132"/>
-      <c r="P34" s="132"/>
-      <c r="Q34" s="132"/>
-      <c r="R34" s="133"/>
+      <c r="B34" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="145"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="145"/>
+      <c r="G34" s="145"/>
+      <c r="H34" s="145"/>
+      <c r="I34" s="145"/>
+      <c r="J34" s="145"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="145"/>
+      <c r="M34" s="145"/>
+      <c r="N34" s="145"/>
+      <c r="O34" s="145"/>
+      <c r="P34" s="145"/>
+      <c r="Q34" s="145"/>
+      <c r="R34" s="146"/>
     </row>
     <row r="35" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="132" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="132"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="132"/>
-      <c r="G35" s="132"/>
-      <c r="H35" s="132"/>
-      <c r="I35" s="132"/>
-      <c r="J35" s="132"/>
-      <c r="K35" s="132"/>
-      <c r="L35" s="132"/>
-      <c r="M35" s="132"/>
-      <c r="N35" s="132"/>
-      <c r="O35" s="132"/>
-      <c r="P35" s="132"/>
-      <c r="Q35" s="132"/>
-      <c r="R35" s="133"/>
+      <c r="B35" s="142"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="32"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="M35" s="32"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="34"/>
     </row>
     <row r="36" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="137"/>
-      <c r="C36" s="33"/>
+      <c r="B36" s="142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="32"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
       <c r="H36" s="34"/>
-      <c r="I36" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="J36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="32"/>
       <c r="K36" s="34"/>
-      <c r="L36" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="M36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="32"/>
       <c r="N36" s="34"/>
-      <c r="O36" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
       <c r="R36" s="34"/>
     </row>
     <row r="37" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="33"/>
+      <c r="B37" s="142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="32"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
       <c r="H37" s="34"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="32"/>
       <c r="K37" s="34"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="32"/>
       <c r="N37" s="34"/>
-      <c r="O37" s="41"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
       <c r="R37" s="34"/>
     </row>
     <row r="38" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="137" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="33"/>
+      <c r="B38" s="142" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="32"/>
       <c r="D38" s="34"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
       <c r="H38" s="34"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="32"/>
       <c r="K38" s="34"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="32"/>
       <c r="N38" s="34"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
       <c r="R38" s="34"/>
     </row>
-    <row r="39" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="137" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="33"/>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="142" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="32"/>
       <c r="D39" s="34"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
       <c r="H39" s="34"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="32"/>
       <c r="K39" s="34"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="32"/>
       <c r="N39" s="34"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
       <c r="R39" s="34"/>
     </row>
-    <row r="40" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="137" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="41"/>
-      <c r="M40" s="33"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="41"/>
-      <c r="P40" s="33"/>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="34"/>
-    </row>
-    <row r="41" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="41" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="138" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32"/>
+      <c r="N41" s="32"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="34"/>
+    </row>
     <row r="42" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="138" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
+      <c r="B42" s="139" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="144"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
       <c r="R42" s="34"/>
     </row>
     <row r="43" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="136" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
+      <c r="B43" s="139" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
       <c r="L43" s="34"/>
-      <c r="M43" s="144"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
+      <c r="M43" s="41"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
       <c r="R43" s="34"/>
     </row>
     <row r="44" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="136" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
+      <c r="B44" s="139" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
       <c r="L44" s="34"/>
-      <c r="M44" s="38"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
+      <c r="M44" s="33"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
       <c r="R44" s="34"/>
     </row>
     <row r="45" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="136" t="s">
-        <v>37</v>
-      </c>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
+      <c r="B45" s="139" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
       <c r="L45" s="34"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="33"/>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="34"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="87"/>
+      <c r="Q45" s="87"/>
+      <c r="R45" s="99"/>
     </row>
     <row r="46" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="136" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="33"/>
-      <c r="O46" s="33"/>
-      <c r="P46" s="93"/>
-      <c r="Q46" s="93"/>
-      <c r="R46" s="100"/>
-    </row>
-    <row r="47" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="134" t="s">
+      <c r="B46" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="135"/>
-      <c r="D47" s="135"/>
-      <c r="E47" s="135"/>
-      <c r="F47" s="135"/>
-      <c r="G47" s="135"/>
-      <c r="H47" s="135"/>
-      <c r="I47" s="135"/>
-      <c r="J47" s="135"/>
-      <c r="K47" s="135"/>
-      <c r="L47" s="100"/>
-      <c r="M47" s="107" t="s">
-        <v>274</v>
-      </c>
-      <c r="N47" s="92"/>
-      <c r="O47" s="92"/>
-      <c r="P47" s="92"/>
-      <c r="Q47" s="92"/>
-      <c r="R47" s="145"/>
-    </row>
-    <row r="48" spans="2:18" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
-      <c r="K48" s="73"/>
+      <c r="C46" s="149"/>
+      <c r="D46" s="149"/>
+      <c r="E46" s="149"/>
+      <c r="F46" s="149"/>
+      <c r="G46" s="149"/>
+      <c r="H46" s="149"/>
+      <c r="I46" s="149"/>
+      <c r="J46" s="149"/>
+      <c r="K46" s="149"/>
+      <c r="L46" s="99"/>
+      <c r="M46" s="92" t="s">
+        <v>284</v>
+      </c>
+      <c r="N46" s="91"/>
+      <c r="O46" s="91"/>
+      <c r="P46" s="91"/>
+      <c r="Q46" s="91"/>
+      <c r="R46" s="133"/>
+    </row>
+    <row r="47" spans="2:18" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="58"/>
+      <c r="K47" s="58"/>
+      <c r="L47" s="101"/>
+      <c r="M47" s="134"/>
+      <c r="N47" s="104"/>
+      <c r="O47" s="104"/>
+      <c r="P47" s="104"/>
+      <c r="Q47" s="104"/>
+      <c r="R47" s="135"/>
+    </row>
+    <row r="48" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="43"/>
       <c r="L48" s="102"/>
-      <c r="M48" s="146"/>
-      <c r="N48" s="86"/>
-      <c r="O48" s="86"/>
-      <c r="P48" s="86"/>
-      <c r="Q48" s="86"/>
-      <c r="R48" s="147"/>
+      <c r="M48" s="42"/>
+      <c r="N48" s="136"/>
+      <c r="O48" s="136"/>
+      <c r="P48" s="136"/>
+      <c r="Q48" s="136"/>
+      <c r="R48" s="137"/>
     </row>
     <row r="49" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="40"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="101"/>
-      <c r="M49" s="39"/>
-      <c r="N49" s="148"/>
-      <c r="O49" s="148"/>
-      <c r="P49" s="148"/>
-      <c r="Q49" s="148"/>
-      <c r="R49" s="149"/>
+      <c r="B49" s="139" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="34"/>
+      <c r="M49" s="33"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="34"/>
     </row>
     <row r="50" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="136" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
+      <c r="B50" s="139" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
       <c r="L50" s="34"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="33"/>
-      <c r="O50" s="33"/>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="33"/>
+      <c r="M50" s="33"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="32"/>
       <c r="R50" s="34"/>
     </row>
-    <row r="51" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="136" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="41"/>
-      <c r="N51" s="33"/>
-      <c r="O51" s="33"/>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="34"/>
-    </row>
   </sheetData>
-  <mergeCells count="90">
-    <mergeCell ref="M47:R49"/>
-    <mergeCell ref="B3:R3"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="B4:R4"/>
-    <mergeCell ref="B22:I22"/>
+  <mergeCells count="89">
+    <mergeCell ref="M50:R50"/>
+    <mergeCell ref="B34:R34"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="B46:L48"/>
+    <mergeCell ref="M49:R49"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="I37:K37"/>
     <mergeCell ref="M45:R45"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="B11:R11"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="B13:R13"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B45:L45"/>
-    <mergeCell ref="M44:R44"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="B16:R16"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="M43:R43"/>
-    <mergeCell ref="N17:R17"/>
+    <mergeCell ref="I38:K38"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B51:L51"/>
-    <mergeCell ref="B12:R12"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="N18:R18"/>
-    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="L36:N36"/>
     <mergeCell ref="B27:N27"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B34:R34"/>
-    <mergeCell ref="N19:R19"/>
-    <mergeCell ref="B14:N14"/>
-    <mergeCell ref="N21:R21"/>
-    <mergeCell ref="B50:L50"/>
-    <mergeCell ref="N20:R20"/>
-    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="B43:L43"/>
     <mergeCell ref="E39:H39"/>
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="B30:R30"/>
-    <mergeCell ref="B24:R24"/>
-    <mergeCell ref="B33:R33"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="B41:R41"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B5:N5"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B18:G18"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="B25:R25"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B24:R24"/>
     <mergeCell ref="H21:M21"/>
     <mergeCell ref="O9:R9"/>
     <mergeCell ref="B7:N7"/>
@@ -6944,32 +7052,73 @@
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B15:R15"/>
     <mergeCell ref="B19:G19"/>
-    <mergeCell ref="M51:R51"/>
-    <mergeCell ref="B35:R35"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="B47:L49"/>
-    <mergeCell ref="M50:R50"/>
-    <mergeCell ref="B43:L43"/>
-    <mergeCell ref="O40:R40"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="M46:R46"/>
+    <mergeCell ref="B25:N25"/>
+    <mergeCell ref="B29:R29"/>
+    <mergeCell ref="B23:R23"/>
+    <mergeCell ref="B32:R32"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="B50:L50"/>
+    <mergeCell ref="B12:R12"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="N18:R18"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B33:R33"/>
+    <mergeCell ref="N19:R19"/>
+    <mergeCell ref="B14:N14"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="B49:L49"/>
+    <mergeCell ref="N20:R20"/>
     <mergeCell ref="I39:K39"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="M43:R43"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="B16:R16"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="M42:R42"/>
+    <mergeCell ref="N17:R17"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="M46:R48"/>
+    <mergeCell ref="B3:R3"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="B4:R4"/>
+    <mergeCell ref="M44:R44"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="B11:R11"/>
+    <mergeCell ref="I36:K36"/>
     <mergeCell ref="L37:N37"/>
-    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="B13:R13"/>
+    <mergeCell ref="B45:L45"/>
     <mergeCell ref="B44:L44"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="B42:R42"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O10:R10" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"여,부"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B34:R34" xr:uid="{0CDFCEB9-8DB1-406A-A79B-94E925622902}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:R33" xr:uid="{0CDFCEB9-8DB1-406A-A79B-94E925622902}">
       <formula1>"□ 신고대상 사업연도에 대한 최소적용제외 특례 선택, ■ 신고대상 사업연도에 대한 최소적용제외 특례 선택"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35:R35" xr:uid="{36B5953F-92F6-4B6B-9E8E-26283ABAFC86}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B34:R34" xr:uid="{36B5953F-92F6-4B6B-9E8E-26283ABAFC86}">
       <formula1>"□ 중요성이 낮은 구성기업에 대한 간소화 계산을 하는 경우 - 중요성이 낮은 구성기업 외의 일반 구성기업에 대한 최소적용제외 특례 선택,■ 중요성이 낮은 구성기업에 대한 간소화 계산을 하는 경우 - 중요성이 낮은 구성기업 외의 일반 구성기업에 대한 최소적용제외 특례 선택"</formula1>
     </dataValidation>
   </dataValidations>
